--- a/templates/schedule_julmarknad.xlsx
+++ b/templates/schedule_julmarknad.xlsx
@@ -1,35 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C.Winkler\Jupyter\WebShopReport\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulfhk\Documents\Svenska Kyrkan\Kyrkan aktuell\0. Events\Click n Collect\Julmarknad - Webbshop\Webbshop Julmarknad 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C077C6AC-F889-4A43-B70A-D7D304DF3B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD7A73E-EE19-4938-B5BC-E0AF5706F47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schema" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -370,13 +359,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C4CDD5-4327-475C-B13C-F4CCF766ADC7}">
-  <dimension ref="A1:B44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -384,348 +373,356 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B2" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B3" s="1">
-        <v>0.51388888888888884</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.53472222222222221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B4" s="1">
-        <v>0.52777777777777779</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.54861111111111105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B5" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.56249999999999989</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B6" s="1">
-        <v>0.55555555555555558</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.57638888888888873</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B7" s="1">
-        <v>0.56944444444444442</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.59027777777777757</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B8" s="1">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.60416666666666641</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B9" s="1">
-        <v>0.59722222222222221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.61805555555555525</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B10" s="1">
-        <v>0.61111111111111116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.63194444444444409</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>45990</v>
+        <v>46354</v>
       </c>
       <c r="B11" s="1">
+        <v>0.64583333333333293</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>46354</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.65972222222222177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>46354</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.67361111111111061</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>46354</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.68749999999999944</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>46354</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.70138888888888828</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>46354</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.71527777777777712</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>46354</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.72916666666666596</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>46354</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.7430555555555548</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.53472222222222221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.54861111111111105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0.56249999999999989</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0.57638888888888873</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0.59027777777777757</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0.60416666666666641</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0.61805555555555525</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0.63194444444444409</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0.64583333333333293</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0.65972222222222177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0.67361111111111061</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0.68749999999999944</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0.70138888888888828</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.71527777777777712</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.72916666666666596</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.7430555555555548</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>46356</v>
+      </c>
+      <c r="B36" s="1">
         <v>0.625</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>45990</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>46356</v>
+      </c>
+      <c r="B37" s="1">
         <v>0.63888888888888884</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>45990</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.65277777777777779</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>45990</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>45990</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0.68055555555555558</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>45990</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0.69444444444444442</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>45990</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>45990</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.72222222222222221</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>45990</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.73611111111111116</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.55555555555555558</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.56944444444444442</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.59722222222222221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.61111111111111116</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B26" s="1">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>46356</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.65277777777777768</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <v>46356</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.66666666666666652</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>46356</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.68055555555555536</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <v>46356</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.6944444444444442</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>46356</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0.70833333333333304</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <v>46356</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.72222222222222188</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <v>46356</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0.73611111111111072</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <v>46380</v>
+      </c>
+      <c r="B45" s="1">
         <v>0.625</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B27" s="1">
-        <v>0.63888888888888884</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0.65277777777777779</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0.68055555555555558</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0.69444444444444442</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.72222222222222221</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
-        <v>45991</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.73611111111111116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>45992</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <v>45992</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0.63888888888888884</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
-        <v>45992</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0.65277777777777779</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <v>45992</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <v>45992</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.68055555555555558</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>45992</v>
-      </c>
-      <c r="B40" s="1">
-        <v>0.69444444444444442</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>45992</v>
-      </c>
-      <c r="B41" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>45992</v>
-      </c>
-      <c r="B42" s="1">
-        <v>0.72222222222222221</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>45992</v>
-      </c>
-      <c r="B43" s="1">
-        <v>0.73611111111111116</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>46022</v>
-      </c>
-      <c r="B44" s="1">
-        <v>0.875</v>
       </c>
     </row>
   </sheetData>
